--- a/EXP/400_50_Unet_smooth0.001/results/train/val_result.xlsx
+++ b/EXP/400_50_Unet_smooth0.001/results/train/val_result.xlsx
@@ -450,13 +450,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.27705</v>
+        <v>1.26489</v>
       </c>
       <c r="C2" t="n">
-        <v>0.44156</v>
+        <v>0.49122</v>
       </c>
       <c r="D2" t="n">
-        <v>0.56954</v>
+        <v>0.6148</v>
       </c>
     </row>
     <row r="3">
@@ -464,13 +464,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.21165</v>
+        <v>1.2228</v>
       </c>
       <c r="C3" t="n">
-        <v>0.56229</v>
+        <v>0.4956</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6815600000000001</v>
+        <v>0.62053</v>
       </c>
     </row>
     <row r="4">
@@ -478,13 +478,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.1724</v>
+        <v>1.16636</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.58987</v>
       </c>
       <c r="D4" t="n">
-        <v>0.73241</v>
+        <v>0.70718</v>
       </c>
     </row>
     <row r="5">
@@ -492,13 +492,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.12779</v>
+        <v>1.14879</v>
       </c>
       <c r="C5" t="n">
-        <v>0.66121</v>
+        <v>0.6146</v>
       </c>
       <c r="D5" t="n">
-        <v>0.77011</v>
+        <v>0.72868</v>
       </c>
     </row>
     <row r="6">
@@ -506,13 +506,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.09278</v>
+        <v>1.08868</v>
       </c>
       <c r="C6" t="n">
-        <v>0.68015</v>
+        <v>0.68546</v>
       </c>
       <c r="D6" t="n">
-        <v>0.78629</v>
+        <v>0.7908500000000001</v>
       </c>
     </row>
     <row r="7">
@@ -520,13 +520,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.05076</v>
+        <v>1.06025</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7045400000000001</v>
+        <v>0.6837299999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.80658</v>
+        <v>0.78948</v>
       </c>
     </row>
     <row r="8">
@@ -534,13 +534,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.00426</v>
+        <v>1.0354</v>
       </c>
       <c r="C8" t="n">
-        <v>0.72367</v>
+        <v>0.6753400000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.82173</v>
+        <v>0.7826</v>
       </c>
     </row>
     <row r="9">
@@ -548,13 +548,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.96021</v>
+        <v>0.99615</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7220800000000001</v>
+        <v>0.70367</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8208299999999999</v>
+        <v>0.80611</v>
       </c>
     </row>
     <row r="10">
@@ -562,13 +562,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.92326</v>
+        <v>0.9484900000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>0.73659</v>
+        <v>0.73097</v>
       </c>
       <c r="D10" t="n">
-        <v>0.83219</v>
+        <v>0.82804</v>
       </c>
     </row>
     <row r="11">
@@ -576,13 +576,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.89139</v>
+        <v>0.92352</v>
       </c>
       <c r="C11" t="n">
-        <v>0.73422</v>
+        <v>0.7327</v>
       </c>
       <c r="D11" t="n">
-        <v>0.83031</v>
+        <v>0.82925</v>
       </c>
     </row>
     <row r="12">
@@ -590,13 +590,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8507400000000001</v>
+        <v>0.88373</v>
       </c>
       <c r="C12" t="n">
-        <v>0.76829</v>
+        <v>0.74091</v>
       </c>
       <c r="D12" t="n">
-        <v>0.85648</v>
+        <v>0.83589</v>
       </c>
     </row>
     <row r="13">
@@ -604,13 +604,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.82241</v>
+        <v>0.86566</v>
       </c>
       <c r="C13" t="n">
-        <v>0.76646</v>
+        <v>0.75568</v>
       </c>
       <c r="D13" t="n">
-        <v>0.85512</v>
+        <v>0.847</v>
       </c>
     </row>
     <row r="14">
@@ -618,13 +618,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.79742</v>
+        <v>0.83306</v>
       </c>
       <c r="C14" t="n">
-        <v>0.77249</v>
+        <v>0.76562</v>
       </c>
       <c r="D14" t="n">
-        <v>0.85938</v>
+        <v>0.85448</v>
       </c>
     </row>
     <row r="15">
@@ -632,13 +632,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.77411</v>
+        <v>0.81169</v>
       </c>
       <c r="C15" t="n">
-        <v>0.78307</v>
+        <v>0.76183</v>
       </c>
       <c r="D15" t="n">
-        <v>0.86721</v>
+        <v>0.85171</v>
       </c>
     </row>
     <row r="16">
@@ -646,13 +646,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.75566</v>
+        <v>0.77544</v>
       </c>
       <c r="C16" t="n">
-        <v>0.78328</v>
+        <v>0.79197</v>
       </c>
       <c r="D16" t="n">
-        <v>0.86722</v>
+        <v>0.87382</v>
       </c>
     </row>
     <row r="17">
@@ -660,13 +660,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.71261</v>
+        <v>0.7595499999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8125599999999999</v>
+        <v>0.7898500000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8881</v>
+        <v>0.87225</v>
       </c>
     </row>
     <row r="18">
@@ -674,13 +674,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.70505</v>
+        <v>0.73508</v>
       </c>
       <c r="C18" t="n">
-        <v>0.80045</v>
+        <v>0.79527</v>
       </c>
       <c r="D18" t="n">
-        <v>0.87965</v>
+        <v>0.87607</v>
       </c>
     </row>
     <row r="19">
@@ -688,13 +688,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.69912</v>
+        <v>0.7285199999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>0.80153</v>
+        <v>0.78921</v>
       </c>
       <c r="D19" t="n">
-        <v>0.88027</v>
+        <v>0.87166</v>
       </c>
     </row>
     <row r="20">
@@ -702,13 +702,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.66943</v>
+        <v>0.69598</v>
       </c>
       <c r="C20" t="n">
-        <v>0.80971</v>
+        <v>0.80432</v>
       </c>
       <c r="D20" t="n">
-        <v>0.88618</v>
+        <v>0.88269</v>
       </c>
     </row>
     <row r="21">
@@ -716,13 +716,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.65817</v>
+        <v>0.67436</v>
       </c>
       <c r="C21" t="n">
-        <v>0.81798</v>
+        <v>0.81598</v>
       </c>
       <c r="D21" t="n">
-        <v>0.89185</v>
+        <v>0.89075</v>
       </c>
     </row>
     <row r="22">
@@ -730,13 +730,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0.63842</v>
+        <v>0.66764</v>
       </c>
       <c r="C22" t="n">
-        <v>0.81347</v>
+        <v>0.80183</v>
       </c>
       <c r="D22" t="n">
-        <v>0.889</v>
+        <v>0.88086</v>
       </c>
     </row>
     <row r="23">
@@ -744,13 +744,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.6321</v>
+        <v>0.65543</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8172199999999999</v>
+        <v>0.81312</v>
       </c>
       <c r="D23" t="n">
-        <v>0.89147</v>
+        <v>0.88884</v>
       </c>
     </row>
     <row r="24">
@@ -758,13 +758,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0.62447</v>
+        <v>0.64219</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8154</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8892099999999999</v>
+        <v>0.89035</v>
       </c>
     </row>
     <row r="25">
@@ -772,13 +772,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>0.62119</v>
+        <v>0.63204</v>
       </c>
       <c r="C25" t="n">
-        <v>0.82529</v>
+        <v>0.82033</v>
       </c>
       <c r="D25" t="n">
-        <v>0.89682</v>
+        <v>0.89377</v>
       </c>
     </row>
     <row r="26">
@@ -786,13 +786,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>0.60542</v>
+        <v>0.62161</v>
       </c>
       <c r="C26" t="n">
-        <v>0.83174</v>
+        <v>0.81843</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9013099999999999</v>
+        <v>0.89257</v>
       </c>
     </row>
     <row r="27">
@@ -800,13 +800,13 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>0.60099</v>
+        <v>0.6194</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8306</v>
+        <v>0.8253200000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>0.90045</v>
+        <v>0.89708</v>
       </c>
     </row>
     <row r="28">
@@ -814,13 +814,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>0.5956900000000001</v>
+        <v>0.60295</v>
       </c>
       <c r="C28" t="n">
-        <v>0.83225</v>
+        <v>0.82542</v>
       </c>
       <c r="D28" t="n">
-        <v>0.90162</v>
+        <v>0.89734</v>
       </c>
     </row>
     <row r="29">
@@ -828,13 +828,13 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>0.59446</v>
+        <v>0.60695</v>
       </c>
       <c r="C29" t="n">
-        <v>0.83013</v>
+        <v>0.82351</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9003100000000001</v>
+        <v>0.89596</v>
       </c>
     </row>
     <row r="30">
@@ -842,13 +842,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>0.58665</v>
+        <v>0.62658</v>
       </c>
       <c r="C30" t="n">
-        <v>0.83419</v>
+        <v>0.81071</v>
       </c>
       <c r="D30" t="n">
-        <v>0.90298</v>
+        <v>0.88663</v>
       </c>
     </row>
     <row r="31">
@@ -856,13 +856,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>0.5722699999999999</v>
+        <v>0.58717</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8374200000000001</v>
+        <v>0.83529</v>
       </c>
       <c r="D31" t="n">
-        <v>0.90523</v>
+        <v>0.90388</v>
       </c>
     </row>
     <row r="32">
@@ -870,13 +870,13 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>0.57886</v>
+        <v>0.58462</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8363699999999999</v>
+        <v>0.83594</v>
       </c>
       <c r="D32" t="n">
-        <v>0.90442</v>
+        <v>0.90428</v>
       </c>
     </row>
     <row r="33">
@@ -884,13 +884,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>0.57263</v>
+        <v>0.57699</v>
       </c>
       <c r="C33" t="n">
-        <v>0.83945</v>
+        <v>0.83653</v>
       </c>
       <c r="D33" t="n">
-        <v>0.90651</v>
+        <v>0.90476</v>
       </c>
     </row>
     <row r="34">
@@ -898,13 +898,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>0.57278</v>
+        <v>0.5743</v>
       </c>
       <c r="C34" t="n">
-        <v>0.83645</v>
+        <v>0.84253</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9045</v>
+        <v>0.90866</v>
       </c>
     </row>
     <row r="35">
@@ -912,13 +912,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>0.59674</v>
+        <v>0.5708299999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>0.82339</v>
+        <v>0.83649</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8953</v>
+        <v>0.90471</v>
       </c>
     </row>
     <row r="36">
@@ -926,13 +926,13 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>0.56756</v>
+        <v>0.58736</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8392500000000001</v>
+        <v>0.82765</v>
       </c>
       <c r="D36" t="n">
-        <v>0.90638</v>
+        <v>0.89857</v>
       </c>
     </row>
     <row r="37">
@@ -940,13 +940,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>0.55836</v>
+        <v>0.56771</v>
       </c>
       <c r="C37" t="n">
-        <v>0.84167</v>
+        <v>0.83845</v>
       </c>
       <c r="D37" t="n">
-        <v>0.90806</v>
+        <v>0.906</v>
       </c>
     </row>
     <row r="38">
@@ -954,13 +954,13 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>0.56292</v>
+        <v>0.56081</v>
       </c>
       <c r="C38" t="n">
-        <v>0.84</v>
+        <v>0.8413</v>
       </c>
       <c r="D38" t="n">
-        <v>0.90696</v>
+        <v>0.90796</v>
       </c>
     </row>
     <row r="39">
@@ -968,13 +968,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>0.5601</v>
+        <v>0.56006</v>
       </c>
       <c r="C39" t="n">
-        <v>0.84376</v>
+        <v>0.8374200000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>0.90935</v>
+        <v>0.90539</v>
       </c>
     </row>
     <row r="40">
@@ -982,13 +982,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>0.57803</v>
+        <v>0.55996</v>
       </c>
       <c r="C40" t="n">
-        <v>0.83591</v>
+        <v>0.8388099999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>0.90398</v>
+        <v>0.90627</v>
       </c>
     </row>
     <row r="41">
@@ -996,13 +996,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>0.56274</v>
+        <v>0.5524</v>
       </c>
       <c r="C41" t="n">
-        <v>0.83344</v>
+        <v>0.84621</v>
       </c>
       <c r="D41" t="n">
-        <v>0.90258</v>
+        <v>0.91113</v>
       </c>
     </row>
     <row r="42">
@@ -1010,13 +1010,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>0.55454</v>
+        <v>0.55398</v>
       </c>
       <c r="C42" t="n">
-        <v>0.84326</v>
+        <v>0.84143</v>
       </c>
       <c r="D42" t="n">
-        <v>0.90907</v>
+        <v>0.90805</v>
       </c>
     </row>
     <row r="43">
@@ -1024,13 +1024,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>0.55871</v>
+        <v>0.5539500000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8420299999999999</v>
+        <v>0.84553</v>
       </c>
       <c r="D43" t="n">
-        <v>0.90825</v>
+        <v>0.91066</v>
       </c>
     </row>
     <row r="44">
@@ -1038,13 +1038,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>0.55913</v>
+        <v>0.55031</v>
       </c>
       <c r="C44" t="n">
-        <v>0.84387</v>
+        <v>0.84623</v>
       </c>
       <c r="D44" t="n">
-        <v>0.90937</v>
+        <v>0.91113</v>
       </c>
     </row>
     <row r="45">
@@ -1052,13 +1052,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>0.55445</v>
+        <v>0.55736</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.83878</v>
       </c>
       <c r="D45" t="n">
-        <v>0.90968</v>
+        <v>0.90621</v>
       </c>
     </row>
     <row r="46">
@@ -1066,13 +1066,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>0.54631</v>
+        <v>0.54365</v>
       </c>
       <c r="C46" t="n">
-        <v>0.84805</v>
+        <v>0.84674</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9121899999999999</v>
+        <v>0.91149</v>
       </c>
     </row>
     <row r="47">
@@ -1080,13 +1080,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>0.5605</v>
+        <v>0.54323</v>
       </c>
       <c r="C47" t="n">
-        <v>0.83578</v>
+        <v>0.85118</v>
       </c>
       <c r="D47" t="n">
-        <v>0.90407</v>
+        <v>0.91435</v>
       </c>
     </row>
     <row r="48">
@@ -1094,13 +1094,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>0.5527300000000001</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="C48" t="n">
-        <v>0.84289</v>
+        <v>0.84626</v>
       </c>
       <c r="D48" t="n">
-        <v>0.90883</v>
+        <v>0.91122</v>
       </c>
     </row>
     <row r="49">
@@ -1108,13 +1108,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>0.5478499999999999</v>
+        <v>0.54496</v>
       </c>
       <c r="C49" t="n">
-        <v>0.84566</v>
+        <v>0.84585</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9105799999999999</v>
+        <v>0.91087</v>
       </c>
     </row>
     <row r="50">
@@ -1122,13 +1122,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>0.54557</v>
+        <v>0.54087</v>
       </c>
       <c r="C50" t="n">
-        <v>0.84906</v>
+        <v>0.8506899999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>0.91283</v>
+        <v>0.9140200000000001</v>
       </c>
     </row>
     <row r="51">
@@ -1136,13 +1136,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>0.54091</v>
+        <v>0.5364</v>
       </c>
       <c r="C51" t="n">
-        <v>0.84922</v>
+        <v>0.8509100000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>0.913</v>
+        <v>0.9142400000000001</v>
       </c>
     </row>
   </sheetData>
